--- a/prix/huot.xlsx
+++ b/prix/huot.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\site-internet\raccords-plomberie\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFDF724-0ABB-4449-BDF0-B7921B1E213C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F386BCFE-25FC-48DF-8D98-77F6CED84D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{B3633BAD-FC45-4A24-8BD9-8C1E06DA75E2}"/>
   </bookViews>
@@ -1073,7 +1073,7 @@
         <v>28</v>
       </c>
       <c r="F16" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1113,7 +1113,7 @@
         <v>32</v>
       </c>
       <c r="F18" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1133,7 +1133,7 @@
         <v>34</v>
       </c>
       <c r="F19" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1233,7 +1233,7 @@
         <v>44</v>
       </c>
       <c r="F24" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/huot.xlsx
+++ b/prix/huot.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F386BCFE-25FC-48DF-8D98-77F6CED84D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782011D4-E37E-4F68-B210-4D3E28E2EA2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{B3633BAD-FC45-4A24-8BD9-8C1E06DA75E2}"/>
   </bookViews>
@@ -401,10 +401,10 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -786,13 +786,13 @@
       <c r="C2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <v>45.54</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="8">
         <v>7</v>
       </c>
     </row>
@@ -806,13 +806,13 @@
       <c r="C3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>40.64</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="8">
         <v>8</v>
       </c>
     </row>
@@ -826,13 +826,13 @@
       <c r="C4" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <v>48.050000000000004</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="8">
         <v>4</v>
       </c>
     </row>
@@ -846,13 +846,13 @@
       <c r="C5" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <v>38.83</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="8">
         <v>4</v>
       </c>
     </row>
@@ -866,13 +866,13 @@
       <c r="C6" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <v>40.18</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <v>9</v>
       </c>
     </row>
@@ -886,13 +886,13 @@
       <c r="C7" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>55.45</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <v>3</v>
       </c>
     </row>
@@ -906,13 +906,13 @@
       <c r="C8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>18.38</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <v>13</v>
       </c>
     </row>
@@ -926,14 +926,14 @@
       <c r="C9" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>18.54</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="7">
-        <v>11</v>
+      <c r="F9" s="8">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -946,14 +946,14 @@
       <c r="C10" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <v>30.060000000000002</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="7">
-        <v>11</v>
+      <c r="F10" s="8">
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -966,14 +966,14 @@
       <c r="C11" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="8">
-        <v>18.38</v>
+      <c r="D11" s="7">
+        <v>16.5</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="7">
-        <v>8</v>
+      <c r="F11" s="8">
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -986,14 +986,14 @@
       <c r="C12" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <v>20.260000000000002</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="7">
-        <v>10</v>
+      <c r="F12" s="8">
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1006,13 +1006,13 @@
       <c r="C13" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <v>29.75</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="8">
         <v>6</v>
       </c>
     </row>
@@ -1026,14 +1026,14 @@
       <c r="C14" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="7">
         <v>15.57</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="7">
-        <v>13</v>
+      <c r="F14" s="8">
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1046,14 +1046,14 @@
       <c r="C15" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="7">
         <v>18.21</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="7">
-        <v>15</v>
+      <c r="F15" s="8">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -1066,13 +1066,13 @@
       <c r="C16" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <v>30.060000000000002</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="8">
         <v>4</v>
       </c>
     </row>
@@ -1086,14 +1086,14 @@
       <c r="C17" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>14.68</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="7">
-        <v>12</v>
+      <c r="F17" s="8">
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1106,14 +1106,14 @@
       <c r="C18" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>20.09</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="7">
-        <v>6</v>
+      <c r="F18" s="8">
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1126,14 +1126,14 @@
       <c r="C19" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="8">
-        <v>32.04</v>
+      <c r="D19" s="7">
+        <v>29.75</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="7">
-        <v>4</v>
+      <c r="F19" s="8">
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1146,13 +1146,13 @@
       <c r="C20" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="7">
         <v>54.58</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1166,13 +1166,13 @@
       <c r="C21" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="7">
         <v>30.93</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="8">
         <v>11</v>
       </c>
     </row>
@@ -1186,14 +1186,14 @@
       <c r="C22" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="7">
         <v>36.590000000000003</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="7">
-        <v>8</v>
+      <c r="F22" s="8">
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -1206,13 +1206,13 @@
       <c r="C23" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="7">
         <v>35.67</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="8">
         <v>2</v>
       </c>
     </row>
@@ -1226,13 +1226,13 @@
       <c r="C24" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="7">
         <v>26.63</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="8">
         <v>4</v>
       </c>
     </row>
@@ -1246,13 +1246,13 @@
       <c r="C25" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="7">
         <v>36.130000000000003</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="8">
         <v>13</v>
       </c>
     </row>
@@ -1266,14 +1266,14 @@
       <c r="C26" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="7">
         <v>51.230000000000004</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="7">
-        <v>1</v>
+      <c r="F26" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -1286,13 +1286,13 @@
       <c r="C27" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="7">
         <v>37.730000000000004</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="8">
         <v>7</v>
       </c>
     </row>
@@ -1306,13 +1306,13 @@
       <c r="C28" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="7">
         <v>35.340000000000003</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="8">
         <v>13</v>
       </c>
     </row>
@@ -1326,13 +1326,13 @@
       <c r="C29" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="7">
         <v>71.14</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="8">
         <v>6</v>
       </c>
     </row>
@@ -1346,13 +1346,13 @@
       <c r="C30" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="7">
         <v>44.21</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="8">
         <v>5</v>
       </c>
     </row>
@@ -1366,13 +1366,13 @@
       <c r="C31" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="7">
         <v>53.09</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="8">
         <v>6</v>
       </c>
     </row>
@@ -1386,13 +1386,13 @@
       <c r="C32" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="7">
         <v>87.05</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="8">
         <v>4</v>
       </c>
     </row>

--- a/prix/huot.xlsx
+++ b/prix/huot.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782011D4-E37E-4F68-B210-4D3E28E2EA2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D314C9-77B9-4BC4-84A1-FA14AFB53896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{B3633BAD-FC45-4A24-8BD9-8C1E06DA75E2}"/>
+    <workbookView xWindow="23124" yWindow="84" windowWidth="19116" windowHeight="10884" xr2:uid="{B3633BAD-FC45-4A24-8BD9-8C1E06DA75E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -913,7 +913,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="8">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1033,7 +1033,7 @@
         <v>24</v>
       </c>
       <c r="F14" s="8">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1053,7 +1053,7 @@
         <v>26</v>
       </c>
       <c r="F15" s="8">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -1093,7 +1093,7 @@
         <v>30</v>
       </c>
       <c r="F17" s="8">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1193,7 +1193,7 @@
         <v>40</v>
       </c>
       <c r="F22" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -1233,7 +1233,7 @@
         <v>44</v>
       </c>
       <c r="F24" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/huot.xlsx
+++ b/prix/huot.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D314C9-77B9-4BC4-84A1-FA14AFB53896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E46471D-39A1-4BD2-B6CB-4BE24508653C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23124" yWindow="84" windowWidth="19116" windowHeight="10884" xr2:uid="{B3633BAD-FC45-4A24-8BD9-8C1E06DA75E2}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{B3633BAD-FC45-4A24-8BD9-8C1E06DA75E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -873,7 +873,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -913,7 +913,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="8">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -933,7 +933,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -953,7 +953,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="8">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -993,7 +993,7 @@
         <v>20</v>
       </c>
       <c r="F12" s="8">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1033,7 +1033,7 @@
         <v>24</v>
       </c>
       <c r="F14" s="8">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1053,7 +1053,7 @@
         <v>26</v>
       </c>
       <c r="F15" s="8">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -1073,7 +1073,7 @@
         <v>28</v>
       </c>
       <c r="F16" s="8">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1113,7 +1113,7 @@
         <v>32</v>
       </c>
       <c r="F18" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1193,7 +1193,7 @@
         <v>40</v>
       </c>
       <c r="F22" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/huot.xlsx
+++ b/prix/huot.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E46471D-39A1-4BD2-B6CB-4BE24508653C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D564322-3509-4865-B434-6330B23396D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{B3633BAD-FC45-4A24-8BD9-8C1E06DA75E2}"/>
   </bookViews>
@@ -853,7 +853,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -873,7 +873,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -913,7 +913,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="8">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -933,7 +933,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="8">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1013,7 +1013,7 @@
         <v>22</v>
       </c>
       <c r="F13" s="8">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1033,7 +1033,7 @@
         <v>24</v>
       </c>
       <c r="F14" s="8">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1053,7 +1053,7 @@
         <v>26</v>
       </c>
       <c r="F15" s="8">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -1073,7 +1073,7 @@
         <v>28</v>
       </c>
       <c r="F16" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1093,7 +1093,7 @@
         <v>30</v>
       </c>
       <c r="F17" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1113,7 +1113,7 @@
         <v>32</v>
       </c>
       <c r="F18" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1173,7 +1173,7 @@
         <v>38</v>
       </c>
       <c r="F21" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1193,7 +1193,7 @@
         <v>40</v>
       </c>
       <c r="F22" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -1233,7 +1233,7 @@
         <v>44</v>
       </c>
       <c r="F24" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -1253,7 +1253,7 @@
         <v>46</v>
       </c>
       <c r="F25" s="8">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1333,7 +1333,7 @@
         <v>54</v>
       </c>
       <c r="F29" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
